--- a/tests/golden/forecast.xlsx
+++ b/tests/golden/forecast.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Assumptions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="P&amp;L" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,14 +17,21 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="2">
@@ -47,8 +54,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -421,107 +430,105 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Periods</t>
         </is>
       </c>
-      <c r="B1" t="n">
+      <c r="B1" s="1" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Start Date</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
+      <c r="B2" s="2" t="n">
+        <v>45658</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Starting Revenue ($)</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="1" t="n">
         <v>1000000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Monthly Growth %</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="M4" t="n">
+      <c r="B4" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="M4" s="1" t="n">
         <v>0.05</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>COGS %</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="1" t="n">
         <v>0.6</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>Tax Rate</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="1" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Horizon End</t>
         </is>
       </c>
-      <c r="B7">
+      <c r="B7" s="2">
         <f>EOMONTH(B2, B1 - 1)</f>
         <v/>
       </c>
@@ -544,331 +551,331 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B1">
+      <c r="B1" s="2">
         <f>Assumptions!B2</f>
         <v/>
       </c>
-      <c r="C1">
+      <c r="C1" s="2">
         <f>EDATE(B1, 1)</f>
         <v/>
       </c>
-      <c r="D1">
+      <c r="D1" s="2">
         <f>EDATE(C1, 1)</f>
         <v/>
       </c>
-      <c r="E1">
+      <c r="E1" s="2">
         <f>EDATE(D1, 1)</f>
         <v/>
       </c>
-      <c r="F1">
+      <c r="F1" s="2">
         <f>EDATE(E1, 1)</f>
         <v/>
       </c>
-      <c r="G1">
+      <c r="G1" s="2">
         <f>EDATE(F1, 1)</f>
         <v/>
       </c>
-      <c r="H1">
+      <c r="H1" s="2">
         <f>EDATE(G1, 1)</f>
         <v/>
       </c>
-      <c r="I1">
+      <c r="I1" s="2">
         <f>EDATE(H1, 1)</f>
         <v/>
       </c>
-      <c r="J1">
+      <c r="J1" s="2">
         <f>EDATE(I1, 1)</f>
         <v/>
       </c>
-      <c r="K1">
+      <c r="K1" s="2">
         <f>EDATE(J1, 1)</f>
         <v/>
       </c>
-      <c r="L1">
+      <c r="L1" s="2">
         <f>EDATE(K1, 1)</f>
         <v/>
       </c>
-      <c r="M1">
+      <c r="M1" s="2">
         <f>EDATE(L1, 1)</f>
         <v/>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B2">
+      <c r="B2" s="1">
         <f>Assumptions!B3</f>
         <v/>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <f>B2 * (1 + Assumptions!C4)</f>
         <v/>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <f>C2 * (1 + Assumptions!D4)</f>
         <v/>
       </c>
-      <c r="E2">
+      <c r="E2" s="1">
         <f>D2 * (1 + Assumptions!E4)</f>
         <v/>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <f>E2 * (1 + Assumptions!F4)</f>
         <v/>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <f>F2 * (1 + Assumptions!G4)</f>
         <v/>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <f>G2 * (1 + Assumptions!H4)</f>
         <v/>
       </c>
-      <c r="I2">
+      <c r="I2" s="1">
         <f>H2 * (1 + Assumptions!I4)</f>
         <v/>
       </c>
-      <c r="J2">
+      <c r="J2" s="1">
         <f>I2 * (1 + Assumptions!J4)</f>
         <v/>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <f>J2 * (1 + Assumptions!K4)</f>
         <v/>
       </c>
-      <c r="L2">
+      <c r="L2" s="1">
         <f>K2 * (1 + Assumptions!L4)</f>
         <v/>
       </c>
-      <c r="M2">
+      <c r="M2" s="1">
         <f>L2 * (1 + Assumptions!M4)</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>COGS</t>
         </is>
       </c>
-      <c r="B3">
+      <c r="B3" s="1">
         <f>B2 * Assumptions!B5</f>
         <v/>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <f>C2 * Assumptions!B5</f>
         <v/>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <f>D2 * Assumptions!B5</f>
         <v/>
       </c>
-      <c r="E3">
+      <c r="E3" s="1">
         <f>E2 * Assumptions!B5</f>
         <v/>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <f>F2 * Assumptions!B5</f>
         <v/>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <f>G2 * Assumptions!B5</f>
         <v/>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <f>H2 * Assumptions!B5</f>
         <v/>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <f>I2 * Assumptions!B5</f>
         <v/>
       </c>
-      <c r="J3">
+      <c r="J3" s="1">
         <f>J2 * Assumptions!B5</f>
         <v/>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <f>K2 * Assumptions!B5</f>
         <v/>
       </c>
-      <c r="L3">
+      <c r="L3" s="1">
         <f>L2 * Assumptions!B5</f>
         <v/>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <f>M2 * Assumptions!B5</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Gross</t>
         </is>
       </c>
-      <c r="B4">
+      <c r="B4" s="1">
         <f>B2 - B3</f>
         <v/>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <f>C2 - C3</f>
         <v/>
       </c>
-      <c r="D4">
+      <c r="D4" s="1">
         <f>D2 - D3</f>
         <v/>
       </c>
-      <c r="E4">
+      <c r="E4" s="1">
         <f>E2 - E3</f>
         <v/>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <f>F2 - F3</f>
         <v/>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <f>G2 - G3</f>
         <v/>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <f>H2 - H3</f>
         <v/>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <f>I2 - I3</f>
         <v/>
       </c>
-      <c r="J4">
+      <c r="J4" s="1">
         <f>J2 - J3</f>
         <v/>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <f>K2 - K3</f>
         <v/>
       </c>
-      <c r="L4">
+      <c r="L4" s="1">
         <f>L2 - L3</f>
         <v/>
       </c>
-      <c r="M4">
+      <c r="M4" s="1">
         <f>M2 - M3</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Taxes</t>
         </is>
       </c>
-      <c r="B5">
+      <c r="B5" s="1">
         <f>B4 * Assumptions!B6</f>
         <v/>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <f>C4 * Assumptions!B6</f>
         <v/>
       </c>
-      <c r="D5">
+      <c r="D5" s="1">
         <f>D4 * Assumptions!B6</f>
         <v/>
       </c>
-      <c r="E5">
+      <c r="E5" s="1">
         <f>E4 * Assumptions!B6</f>
         <v/>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <f>F4 * Assumptions!B6</f>
         <v/>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <f>G4 * Assumptions!B6</f>
         <v/>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <f>H4 * Assumptions!B6</f>
         <v/>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <f>I4 * Assumptions!B6</f>
         <v/>
       </c>
-      <c r="J5">
+      <c r="J5" s="1">
         <f>J4 * Assumptions!B6</f>
         <v/>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <f>K4 * Assumptions!B6</f>
         <v/>
       </c>
-      <c r="L5">
+      <c r="L5" s="1">
         <f>L4 * Assumptions!B6</f>
         <v/>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <f>M4 * Assumptions!B6</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="B6">
+      <c r="B6" s="1">
         <f>B4 - B5</f>
         <v/>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <f>C4 - C5</f>
         <v/>
       </c>
-      <c r="D6">
+      <c r="D6" s="1">
         <f>D4 - D5</f>
         <v/>
       </c>
-      <c r="E6">
+      <c r="E6" s="1">
         <f>E4 - E5</f>
         <v/>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <f>F4 - F5</f>
         <v/>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <f>G4 - G5</f>
         <v/>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <f>H4 - H5</f>
         <v/>
       </c>
-      <c r="I6">
+      <c r="I6" s="1">
         <f>I4 - I5</f>
         <v/>
       </c>
-      <c r="J6">
+      <c r="J6" s="1">
         <f>J4 - J5</f>
         <v/>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <f>K4 - K5</f>
         <v/>
       </c>
-      <c r="L6">
+      <c r="L6" s="1">
         <f>L4 - L5</f>
         <v/>
       </c>
-      <c r="M6">
+      <c r="M6" s="1">
         <f>M4 - M5</f>
         <v/>
       </c>

--- a/tests/golden/forecast.xlsx
+++ b/tests/golden/forecast.xlsx
@@ -530,11 +530,14 @@
       </c>
       <c r="B7" s="2">
         <f>EOMONTH(B2, B1 - 1)</f>
-        <v/>
+        <v>46022</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError sqref="B7" formula="1" formulaRange="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -547,7 +550,7 @@
   <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -558,329 +561,332 @@
       </c>
       <c r="B1" s="2">
         <f>Assumptions!B2</f>
-        <v/>
+        <v>45658</v>
       </c>
       <c r="C1" s="2">
         <f>EDATE(B1, 1)</f>
-        <v/>
+        <v>45689</v>
       </c>
       <c r="D1" s="2">
         <f>EDATE(C1, 1)</f>
-        <v/>
+        <v>45717</v>
       </c>
       <c r="E1" s="2">
         <f>EDATE(D1, 1)</f>
-        <v/>
+        <v>45748</v>
       </c>
       <c r="F1" s="2">
         <f>EDATE(E1, 1)</f>
-        <v/>
+        <v>45778</v>
       </c>
       <c r="G1" s="2">
         <f>EDATE(F1, 1)</f>
-        <v/>
+        <v>45809</v>
       </c>
       <c r="H1" s="2">
         <f>EDATE(G1, 1)</f>
-        <v/>
+        <v>45839</v>
       </c>
       <c r="I1" s="2">
         <f>EDATE(H1, 1)</f>
-        <v/>
+        <v>45870</v>
       </c>
       <c r="J1" s="2">
         <f>EDATE(I1, 1)</f>
-        <v/>
+        <v>45901</v>
       </c>
       <c r="K1" s="2">
         <f>EDATE(J1, 1)</f>
-        <v/>
+        <v>45931</v>
       </c>
       <c r="L1" s="2">
         <f>EDATE(K1, 1)</f>
-        <v/>
+        <v>45962</v>
       </c>
       <c r="M1" s="2">
         <f>EDATE(L1, 1)</f>
-        <v/>
+        <v>45992</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Revenue ($)</t>
         </is>
       </c>
       <c r="B2" s="1">
         <f>Assumptions!B3</f>
-        <v/>
+        <v>1000000</v>
       </c>
       <c r="C2" s="1">
         <f>B2 * (1 + Assumptions!C4)</f>
-        <v/>
+        <v>1050000</v>
       </c>
       <c r="D2" s="1">
         <f>C2 * (1 + Assumptions!D4)</f>
-        <v/>
+        <v>1102500</v>
       </c>
       <c r="E2" s="1">
         <f>D2 * (1 + Assumptions!E4)</f>
-        <v/>
+        <v>1157625</v>
       </c>
       <c r="F2" s="1">
         <f>E2 * (1 + Assumptions!F4)</f>
-        <v/>
+        <v>1215506.25</v>
       </c>
       <c r="G2" s="1">
         <f>F2 * (1 + Assumptions!G4)</f>
-        <v/>
+        <v>1276281.5625</v>
       </c>
       <c r="H2" s="1">
         <f>G2 * (1 + Assumptions!H4)</f>
-        <v/>
+        <v>1340095.640625</v>
       </c>
       <c r="I2" s="1">
         <f>H2 * (1 + Assumptions!I4)</f>
-        <v/>
+        <v>1407100.42265625</v>
       </c>
       <c r="J2" s="1">
         <f>I2 * (1 + Assumptions!J4)</f>
-        <v/>
+        <v>1477455.44378906</v>
       </c>
       <c r="K2" s="1">
         <f>J2 * (1 + Assumptions!K4)</f>
-        <v/>
+        <v>1551328.21597852</v>
       </c>
       <c r="L2" s="1">
         <f>K2 * (1 + Assumptions!L4)</f>
-        <v/>
+        <v>1628894.62677744</v>
       </c>
       <c r="M2" s="1">
         <f>L2 * (1 + Assumptions!M4)</f>
-        <v/>
+        <v>1710339.35811631</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>COGS</t>
+          <t>COGS ($)</t>
         </is>
       </c>
       <c r="B3" s="1">
         <f>B2 * Assumptions!B5</f>
-        <v/>
+        <v>600000</v>
       </c>
       <c r="C3" s="1">
         <f>C2 * Assumptions!B5</f>
-        <v/>
+        <v>630000</v>
       </c>
       <c r="D3" s="1">
         <f>D2 * Assumptions!B5</f>
-        <v/>
+        <v>661500</v>
       </c>
       <c r="E3" s="1">
         <f>E2 * Assumptions!B5</f>
-        <v/>
+        <v>694575</v>
       </c>
       <c r="F3" s="1">
         <f>F2 * Assumptions!B5</f>
-        <v/>
+        <v>729303.75</v>
       </c>
       <c r="G3" s="1">
         <f>G2 * Assumptions!B5</f>
-        <v/>
+        <v>765768.9375</v>
       </c>
       <c r="H3" s="1">
         <f>H2 * Assumptions!B5</f>
-        <v/>
+        <v>804057.384375</v>
       </c>
       <c r="I3" s="1">
         <f>I2 * Assumptions!B5</f>
-        <v/>
+        <v>844260.25359375</v>
       </c>
       <c r="J3" s="1">
         <f>J2 * Assumptions!B5</f>
-        <v/>
+        <v>886473.266273438</v>
       </c>
       <c r="K3" s="1">
         <f>K2 * Assumptions!B5</f>
-        <v/>
+        <v>930796.929587109</v>
       </c>
       <c r="L3" s="1">
         <f>L2 * Assumptions!B5</f>
-        <v/>
+        <v>977336.776066465</v>
       </c>
       <c r="M3" s="1">
         <f>M2 * Assumptions!B5</f>
-        <v/>
+        <v>1026203.61486979</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Gross</t>
+          <t>Gross ($)</t>
         </is>
       </c>
       <c r="B4" s="1">
         <f>B2 - B3</f>
-        <v/>
+        <v>400000</v>
       </c>
       <c r="C4" s="1">
         <f>C2 - C3</f>
-        <v/>
+        <v>420000</v>
       </c>
       <c r="D4" s="1">
         <f>D2 - D3</f>
-        <v/>
+        <v>441000</v>
       </c>
       <c r="E4" s="1">
         <f>E2 - E3</f>
-        <v/>
+        <v>463050</v>
       </c>
       <c r="F4" s="1">
         <f>F2 - F3</f>
-        <v/>
+        <v>486202.5</v>
       </c>
       <c r="G4" s="1">
         <f>G2 - G3</f>
-        <v/>
+        <v>510512.625</v>
       </c>
       <c r="H4" s="1">
         <f>H2 - H3</f>
-        <v/>
+        <v>536038.25625</v>
       </c>
       <c r="I4" s="1">
         <f>I2 - I3</f>
-        <v/>
+        <v>562840.1690625</v>
       </c>
       <c r="J4" s="1">
         <f>J2 - J3</f>
-        <v/>
+        <v>590982.177515625</v>
       </c>
       <c r="K4" s="1">
         <f>K2 - K3</f>
-        <v/>
+        <v>620531.286391406</v>
       </c>
       <c r="L4" s="1">
         <f>L2 - L3</f>
-        <v/>
+        <v>651557.850710977</v>
       </c>
       <c r="M4" s="1">
         <f>M2 - M3</f>
-        <v/>
+        <v>684135.743246526</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Taxes</t>
+          <t>Taxes ($)</t>
         </is>
       </c>
       <c r="B5" s="1">
         <f>B4 * Assumptions!B6</f>
-        <v/>
+        <v>100000</v>
       </c>
       <c r="C5" s="1">
         <f>C4 * Assumptions!B6</f>
-        <v/>
+        <v>105000</v>
       </c>
       <c r="D5" s="1">
         <f>D4 * Assumptions!B6</f>
-        <v/>
+        <v>110250</v>
       </c>
       <c r="E5" s="1">
         <f>E4 * Assumptions!B6</f>
-        <v/>
+        <v>115762.5</v>
       </c>
       <c r="F5" s="1">
         <f>F4 * Assumptions!B6</f>
-        <v/>
+        <v>121550.625</v>
       </c>
       <c r="G5" s="1">
         <f>G4 * Assumptions!B6</f>
-        <v/>
+        <v>127628.15625</v>
       </c>
       <c r="H5" s="1">
         <f>H4 * Assumptions!B6</f>
-        <v/>
+        <v>134009.5640625</v>
       </c>
       <c r="I5" s="1">
         <f>I4 * Assumptions!B6</f>
-        <v/>
+        <v>140710.042265625</v>
       </c>
       <c r="J5" s="1">
         <f>J4 * Assumptions!B6</f>
-        <v/>
+        <v>147745.544378906</v>
       </c>
       <c r="K5" s="1">
         <f>K4 * Assumptions!B6</f>
-        <v/>
+        <v>155132.821597852</v>
       </c>
       <c r="L5" s="1">
         <f>L4 * Assumptions!B6</f>
-        <v/>
+        <v>162889.462677744</v>
       </c>
       <c r="M5" s="1">
         <f>M4 * Assumptions!B6</f>
-        <v/>
+        <v>171033.935811631</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Net ($)</t>
         </is>
       </c>
       <c r="B6" s="1">
         <f>B4 - B5</f>
-        <v/>
+        <v>300000</v>
       </c>
       <c r="C6" s="1">
         <f>C4 - C5</f>
-        <v/>
+        <v>315000</v>
       </c>
       <c r="D6" s="1">
         <f>D4 - D5</f>
-        <v/>
+        <v>330750</v>
       </c>
       <c r="E6" s="1">
         <f>E4 - E5</f>
-        <v/>
+        <v>347287.5</v>
       </c>
       <c r="F6" s="1">
         <f>F4 - F5</f>
-        <v/>
+        <v>364651.875</v>
       </c>
       <c r="G6" s="1">
         <f>G4 - G5</f>
-        <v/>
+        <v>382884.46875</v>
       </c>
       <c r="H6" s="1">
         <f>H4 - H5</f>
-        <v/>
+        <v>402028.6921875</v>
       </c>
       <c r="I6" s="1">
         <f>I4 - I5</f>
-        <v/>
+        <v>422130.126796875</v>
       </c>
       <c r="J6" s="1">
         <f>J4 - J5</f>
-        <v/>
+        <v>443236.633136719</v>
       </c>
       <c r="K6" s="1">
         <f>K4 - K5</f>
-        <v/>
+        <v>465398.464793555</v>
       </c>
       <c r="L6" s="1">
         <f>L4 - L5</f>
-        <v/>
+        <v>488668.388033233</v>
       </c>
       <c r="M6" s="1">
         <f>M4 - M5</f>
-        <v/>
+        <v>513101.807434894</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError sqref="B1:M6" formula="1" formulaRange="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>